--- a/depara diretoria.xlsx
+++ b/depara diretoria.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mrvengenhariasa-my.sharepoint.com/personal/laura_storari_mrv_com_br/Documents/6. IA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mrvengenhariasa-my.sharepoint.com/personal/laura_storari_mrv_com_br/Documents/6. IA/Gerados BR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{65FE1AA5-74C4-4A42-A9FA-1452C0EFBA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A87A0C7-8415-41E7-B4FC-60BE0AB8FA69}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{65FE1AA5-74C4-4A42-A9FA-1452C0EFBA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42ABCEB7-6986-4975-96B6-C4D158913657}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F07712CE-26C6-4B07-B0A6-3DF0E73012FB}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="74" r:id="rId2"/>
+    <pivotCache cacheId="29" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2104,7 +2104,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Laura Storari Da Costa" refreshedDate="46293.485608680552" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{E0EF074C-C723-4371-B09E-BB57875EBB2F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Laura Storari Da Costa" refreshedDate="46294.685049421299" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{E0EF074C-C723-4371-B09E-BB57875EBB2F}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="7">
     <cacheField name="[d_Empreendimento].[NomeEmpreendimento].[NomeEmpreendimento]" caption="NomeEmpreendimento" numFmtId="0" hierarchy="42" level="1">
@@ -3382,7 +3382,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B44589E-B7BE-40F4-BD56-FBBF4F927B34}" name="PainelDetalhamentoDePropo" cacheId="74" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B44589E-B7BE-40F4-BD56-FBBF4F927B34}" name="PainelDetalhamentoDePropo" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:E507" firstHeaderRow="1" firstDataRow="1" firstDataCol="4" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -8063,7 +8063,7 @@
         <v>594</v>
       </c>
       <c r="E9" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -8284,7 +8284,7 @@
         <v>592</v>
       </c>
       <c r="E22" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -8301,7 +8301,7 @@
         <v>592</v>
       </c>
       <c r="E23" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -8488,7 +8488,7 @@
         <v>29</v>
       </c>
       <c r="E34" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -8522,7 +8522,7 @@
         <v>29</v>
       </c>
       <c r="E36" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -8607,7 +8607,7 @@
         <v>574</v>
       </c>
       <c r="E41" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -8658,7 +8658,7 @@
         <v>577</v>
       </c>
       <c r="E44" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -8692,7 +8692,7 @@
         <v>574</v>
       </c>
       <c r="E46" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -8743,7 +8743,7 @@
         <v>574</v>
       </c>
       <c r="E49" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -8777,7 +8777,7 @@
         <v>574</v>
       </c>
       <c r="E51" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -8913,7 +8913,7 @@
         <v>567</v>
       </c>
       <c r="E59" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -8981,7 +8981,7 @@
         <v>601</v>
       </c>
       <c r="E63" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -9032,7 +9032,7 @@
         <v>567</v>
       </c>
       <c r="E66" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -9134,7 +9134,7 @@
         <v>562</v>
       </c>
       <c r="E72" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -9304,7 +9304,7 @@
         <v>624</v>
       </c>
       <c r="E82" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -9338,7 +9338,7 @@
         <v>568</v>
       </c>
       <c r="E84" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
@@ -9355,7 +9355,7 @@
         <v>565</v>
       </c>
       <c r="E85" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -9372,7 +9372,7 @@
         <v>596</v>
       </c>
       <c r="E86" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
@@ -9406,7 +9406,7 @@
         <v>642</v>
       </c>
       <c r="E88" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
@@ -9525,7 +9525,7 @@
         <v>596</v>
       </c>
       <c r="E95" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
@@ -9576,7 +9576,7 @@
         <v>642</v>
       </c>
       <c r="E98" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -9661,7 +9661,7 @@
         <v>605</v>
       </c>
       <c r="E103" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -9763,7 +9763,7 @@
         <v>614</v>
       </c>
       <c r="E109" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -9780,7 +9780,7 @@
         <v>562</v>
       </c>
       <c r="E110" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -9882,7 +9882,7 @@
         <v>122</v>
       </c>
       <c r="E116" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -9967,7 +9967,7 @@
         <v>621</v>
       </c>
       <c r="E121" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
@@ -9984,7 +9984,7 @@
         <v>618</v>
       </c>
       <c r="E122" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
@@ -10018,7 +10018,7 @@
         <v>566</v>
       </c>
       <c r="E124" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
@@ -10052,7 +10052,7 @@
         <v>577</v>
       </c>
       <c r="E126" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
@@ -10103,7 +10103,7 @@
         <v>604</v>
       </c>
       <c r="E129" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
@@ -10137,7 +10137,7 @@
         <v>616</v>
       </c>
       <c r="E131" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
@@ -10205,7 +10205,7 @@
         <v>621</v>
       </c>
       <c r="E135" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
@@ -10426,7 +10426,7 @@
         <v>611</v>
       </c>
       <c r="E148" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
@@ -10443,7 +10443,7 @@
         <v>611</v>
       </c>
       <c r="E149" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
@@ -10545,7 +10545,7 @@
         <v>575</v>
       </c>
       <c r="E155" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
@@ -10596,7 +10596,7 @@
         <v>575</v>
       </c>
       <c r="E158" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
@@ -10681,7 +10681,7 @@
         <v>576</v>
       </c>
       <c r="E163" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
@@ -10766,7 +10766,7 @@
         <v>603</v>
       </c>
       <c r="E168" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
@@ -11004,7 +11004,7 @@
         <v>590</v>
       </c>
       <c r="E182" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
@@ -11038,7 +11038,7 @@
         <v>651</v>
       </c>
       <c r="E184" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
@@ -11072,7 +11072,7 @@
         <v>567</v>
       </c>
       <c r="E186" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
@@ -11089,7 +11089,7 @@
         <v>567</v>
       </c>
       <c r="E187" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
@@ -11140,7 +11140,7 @@
         <v>645</v>
       </c>
       <c r="E190" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
@@ -11242,7 +11242,7 @@
         <v>633</v>
       </c>
       <c r="E196" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
@@ -11395,7 +11395,7 @@
         <v>598</v>
       </c>
       <c r="E205" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
@@ -11429,7 +11429,7 @@
         <v>562</v>
       </c>
       <c r="E207" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
@@ -11446,7 +11446,7 @@
         <v>596</v>
       </c>
       <c r="E208" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
@@ -11616,7 +11616,7 @@
         <v>638</v>
       </c>
       <c r="E218" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
@@ -11650,7 +11650,7 @@
         <v>603</v>
       </c>
       <c r="E220" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
@@ -11803,7 +11803,7 @@
         <v>581</v>
       </c>
       <c r="E229" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
@@ -11956,7 +11956,7 @@
         <v>580</v>
       </c>
       <c r="E238" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
@@ -12007,7 +12007,7 @@
         <v>562</v>
       </c>
       <c r="E241" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
@@ -12024,7 +12024,7 @@
         <v>22</v>
       </c>
       <c r="E242" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
@@ -12058,7 +12058,7 @@
         <v>583</v>
       </c>
       <c r="E244" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
@@ -12092,7 +12092,7 @@
         <v>22</v>
       </c>
       <c r="E246" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
@@ -12211,7 +12211,7 @@
         <v>586</v>
       </c>
       <c r="E253" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
@@ -12245,7 +12245,7 @@
         <v>586</v>
       </c>
       <c r="E255" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
@@ -12262,7 +12262,7 @@
         <v>586</v>
       </c>
       <c r="E256" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
@@ -12449,7 +12449,7 @@
         <v>627</v>
       </c>
       <c r="E267" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
@@ -12466,7 +12466,7 @@
         <v>639</v>
       </c>
       <c r="E268" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
@@ -12568,7 +12568,7 @@
         <v>565</v>
       </c>
       <c r="E274" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
@@ -12585,7 +12585,7 @@
         <v>603</v>
       </c>
       <c r="E275" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
@@ -12619,7 +12619,7 @@
         <v>569</v>
       </c>
       <c r="E277" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
@@ -12772,7 +12772,7 @@
         <v>588</v>
       </c>
       <c r="E286" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
@@ -12891,7 +12891,7 @@
         <v>565</v>
       </c>
       <c r="E293" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.35">
@@ -13010,7 +13010,7 @@
         <v>588</v>
       </c>
       <c r="E300" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.35">
@@ -13061,7 +13061,7 @@
         <v>599</v>
       </c>
       <c r="E303" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.35">
@@ -13095,7 +13095,7 @@
         <v>589</v>
       </c>
       <c r="E305" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.35">
@@ -13197,7 +13197,7 @@
         <v>599</v>
       </c>
       <c r="E311" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.35">
@@ -13248,7 +13248,7 @@
         <v>599</v>
       </c>
       <c r="E314" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.35">
@@ -13265,7 +13265,7 @@
         <v>599</v>
       </c>
       <c r="E315" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.35">
@@ -13333,7 +13333,7 @@
         <v>593</v>
       </c>
       <c r="E319" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.35">
@@ -13384,7 +13384,7 @@
         <v>578</v>
       </c>
       <c r="E322" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.35">
@@ -13469,7 +13469,7 @@
         <v>621</v>
       </c>
       <c r="E327" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.35">
@@ -13656,7 +13656,7 @@
         <v>578</v>
       </c>
       <c r="E338" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.35">
@@ -13690,7 +13690,7 @@
         <v>583</v>
       </c>
       <c r="E340" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.35">
@@ -13741,7 +13741,7 @@
         <v>607</v>
       </c>
       <c r="E343" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.35">
@@ -13758,7 +13758,7 @@
         <v>607</v>
       </c>
       <c r="E344" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.35">
@@ -13826,7 +13826,7 @@
         <v>595</v>
       </c>
       <c r="E348" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.35">
@@ -13945,7 +13945,7 @@
         <v>616</v>
       </c>
       <c r="E355" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.35">
@@ -13962,7 +13962,7 @@
         <v>611</v>
       </c>
       <c r="E356" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.35">
@@ -14030,7 +14030,7 @@
         <v>590</v>
       </c>
       <c r="E360" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.35">
@@ -14132,7 +14132,7 @@
         <v>565</v>
       </c>
       <c r="E366" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.35">
@@ -14149,7 +14149,7 @@
         <v>565</v>
       </c>
       <c r="E367" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
@@ -14166,7 +14166,7 @@
         <v>563</v>
       </c>
       <c r="E368" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
@@ -14285,7 +14285,7 @@
         <v>563</v>
       </c>
       <c r="E375" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.35">
@@ -14421,7 +14421,7 @@
         <v>562</v>
       </c>
       <c r="E383" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.35">
@@ -14472,7 +14472,7 @@
         <v>572</v>
       </c>
       <c r="E386" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.35">
@@ -14540,7 +14540,7 @@
         <v>565</v>
       </c>
       <c r="E390" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.35">
@@ -14574,7 +14574,7 @@
         <v>589</v>
       </c>
       <c r="E392" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.35">
@@ -14676,7 +14676,7 @@
         <v>610</v>
       </c>
       <c r="E398" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.35">
@@ -14727,7 +14727,7 @@
         <v>573</v>
       </c>
       <c r="E401" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.35">
@@ -14744,7 +14744,7 @@
         <v>574</v>
       </c>
       <c r="E402" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.35">
@@ -14914,7 +14914,7 @@
         <v>562</v>
       </c>
       <c r="E412" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.35">
@@ -14948,7 +14948,7 @@
         <v>565</v>
       </c>
       <c r="E414" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.35">
@@ -14982,7 +14982,7 @@
         <v>565</v>
       </c>
       <c r="E416" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.35">
@@ -15050,7 +15050,7 @@
         <v>599</v>
       </c>
       <c r="E420" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.35">
@@ -15152,7 +15152,7 @@
         <v>602</v>
       </c>
       <c r="E426" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.35">
@@ -15271,7 +15271,7 @@
         <v>575</v>
       </c>
       <c r="E433" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.35">
@@ -15322,7 +15322,7 @@
         <v>566</v>
       </c>
       <c r="E436" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.35">
@@ -15424,7 +15424,7 @@
         <v>564</v>
       </c>
       <c r="E442" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.35">
@@ -15492,7 +15492,7 @@
         <v>575</v>
       </c>
       <c r="E446" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.35">
@@ -15560,7 +15560,7 @@
         <v>575</v>
       </c>
       <c r="E450" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.35">
@@ -15594,7 +15594,7 @@
         <v>565</v>
       </c>
       <c r="E452" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.35">
@@ -15713,7 +15713,7 @@
         <v>639</v>
       </c>
       <c r="E459" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.35">
@@ -15730,7 +15730,7 @@
         <v>639</v>
       </c>
       <c r="E460" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.35">
@@ -15764,7 +15764,7 @@
         <v>603</v>
       </c>
       <c r="E462" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.35">
@@ -15781,7 +15781,7 @@
         <v>591</v>
       </c>
       <c r="E463" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.35">
@@ -15849,7 +15849,7 @@
         <v>425</v>
       </c>
       <c r="E467" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.35">
@@ -15866,7 +15866,7 @@
         <v>644</v>
       </c>
       <c r="E468" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.35">
@@ -15883,7 +15883,7 @@
         <v>627</v>
       </c>
       <c r="E469" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.35">
@@ -16002,7 +16002,7 @@
         <v>624</v>
       </c>
       <c r="E476" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.35">
@@ -16019,7 +16019,7 @@
         <v>638</v>
       </c>
       <c r="E477" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.35">
@@ -16053,7 +16053,7 @@
         <v>589</v>
       </c>
       <c r="E479" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.35">
@@ -16070,7 +16070,7 @@
         <v>567</v>
       </c>
       <c r="E480" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.35">
@@ -16155,7 +16155,7 @@
         <v>568</v>
       </c>
       <c r="E485" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.35">
@@ -16172,7 +16172,7 @@
         <v>582</v>
       </c>
       <c r="E486" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.35">
@@ -16223,7 +16223,7 @@
         <v>653</v>
       </c>
       <c r="E489" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.35">
@@ -16291,7 +16291,7 @@
         <v>595</v>
       </c>
       <c r="E493" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.35">
@@ -16461,7 +16461,7 @@
         <v>595</v>
       </c>
       <c r="E503" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.35">
@@ -16478,7 +16478,7 @@
         <v>595</v>
       </c>
       <c r="E504" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.35">
@@ -16495,7 +16495,7 @@
         <v>622</v>
       </c>
       <c r="E505" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.35">
@@ -16520,7 +16520,7 @@
         <v>513</v>
       </c>
       <c r="E507" s="2">
-        <v>35801</v>
+        <v>35968</v>
       </c>
     </row>
   </sheetData>
